--- a/00_BIMR/Gantt_graph.xlsx
+++ b/00_BIMR/Gantt_graph.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28324"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Garcilazo\Python\00Exercises\CHEMAI_projects\00_Cameron\FMIP-Evolionics\00_BIMR\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\camgu\Goward\Code\FMIP-Evolionics\00_BIMR\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{6C28ED04-6486-4F00-A570-A34057F17B52}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3F549AF8-5A86-4784-AC7F-97733FB1E8A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="12552" xr2:uid="{89FDD169-2996-45AF-8481-084E55912A13}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="16220" xr2:uid="{89FDD169-2996-45AF-8481-084E55912A13}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
   <si>
     <t>Setup and Data collection</t>
   </si>
@@ -53,50 +53,17 @@
     <t>Documentation and GitHub control</t>
   </si>
   <si>
-    <t>Month_1</t>
+    <t>Results</t>
   </si>
   <si>
-    <t>Month_2</t>
-  </si>
-  <si>
-    <t>Month_3</t>
-  </si>
-  <si>
-    <t>Month_4</t>
-  </si>
-  <si>
-    <t>Month_5</t>
-  </si>
-  <si>
-    <t>Month_6</t>
-  </si>
-  <si>
-    <t>Month_7</t>
-  </si>
-  <si>
-    <t>Month_8</t>
-  </si>
-  <si>
-    <t>Month_9</t>
-  </si>
-  <si>
-    <t>Month_10</t>
-  </si>
-  <si>
-    <t>Month_11</t>
-  </si>
-  <si>
-    <t>Month_12</t>
-  </si>
-  <si>
-    <t>Results</t>
+    <t>Month</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -110,8 +77,14 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="14"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
   </fonts>
-  <fills count="8">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -154,8 +127,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -163,18 +142,65 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right style="thick">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thick">
+        <color indexed="64"/>
+      </right>
+      <top style="thick">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thick">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -509,118 +535,242 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D9D001CD-BA9A-4BDA-BD70-E7A7EE1DF1C1}">
-  <dimension ref="A1:M7"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
+  <dimension ref="A1:N13"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="28.20703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="28.1796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.55000000000000004">
-      <c r="B1" t="s">
+    <row r="1" spans="1:14" ht="18" x14ac:dyDescent="0.4">
+      <c r="A1" s="1"/>
+      <c r="B1" s="1"/>
+      <c r="C1" s="1"/>
+      <c r="D1" s="1"/>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+      <c r="H1" s="1"/>
+      <c r="I1" s="1"/>
+      <c r="J1" s="1"/>
+      <c r="K1" s="1"/>
+      <c r="L1" s="1"/>
+      <c r="M1" s="1"/>
+      <c r="N1" s="1"/>
+    </row>
+    <row r="2" spans="1:14" ht="18.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A2" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" s="14">
+        <v>1</v>
+      </c>
+      <c r="C2" s="14">
+        <v>2</v>
+      </c>
+      <c r="D2" s="14">
+        <v>3</v>
+      </c>
+      <c r="E2" s="14">
+        <v>4</v>
+      </c>
+      <c r="F2" s="14">
         <v>5</v>
       </c>
-      <c r="C1" t="s">
+      <c r="G2" s="14">
         <v>6</v>
       </c>
-      <c r="D1" t="s">
+      <c r="H2" s="14">
         <v>7</v>
       </c>
-      <c r="E1" t="s">
+      <c r="I2" s="14">
         <v>8</v>
       </c>
-      <c r="F1" t="s">
+      <c r="J2" s="14">
         <v>9</v>
       </c>
-      <c r="G1" t="s">
+      <c r="K2" s="14">
         <v>10</v>
       </c>
-      <c r="H1" t="s">
+      <c r="L2" s="14">
         <v>11</v>
       </c>
-      <c r="I1" t="s">
+      <c r="M2" s="14">
         <v>12</v>
       </c>
-      <c r="J1" t="s">
-        <v>13</v>
-      </c>
-      <c r="K1" t="s">
-        <v>14</v>
-      </c>
-      <c r="L1" t="s">
-        <v>15</v>
-      </c>
-      <c r="M1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.55000000000000004">
-      <c r="A2" t="s">
+    </row>
+    <row r="3" spans="1:14" ht="18.5" thickTop="1" x14ac:dyDescent="0.4">
+      <c r="A3" s="13" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="4"/>
-      <c r="C2" s="4"/>
-    </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.55000000000000004">
-      <c r="A3" t="s">
+      <c r="B3" s="2"/>
+      <c r="C3" s="2"/>
+      <c r="D3" s="10"/>
+      <c r="E3" s="10"/>
+      <c r="F3" s="10"/>
+      <c r="G3" s="10"/>
+      <c r="H3" s="10"/>
+      <c r="I3" s="10"/>
+      <c r="J3" s="10"/>
+      <c r="K3" s="10"/>
+      <c r="L3" s="10"/>
+      <c r="M3" s="10"/>
+    </row>
+    <row r="4" spans="1:14" ht="18" x14ac:dyDescent="0.4">
+      <c r="A4" s="12"/>
+      <c r="B4" s="2"/>
+      <c r="C4" s="2"/>
+      <c r="D4" s="10"/>
+      <c r="E4" s="10"/>
+      <c r="F4" s="10"/>
+      <c r="G4" s="10"/>
+      <c r="H4" s="10"/>
+      <c r="I4" s="10"/>
+      <c r="J4" s="10"/>
+      <c r="K4" s="10"/>
+      <c r="L4" s="10"/>
+      <c r="M4" s="10"/>
+    </row>
+    <row r="5" spans="1:14" ht="18" x14ac:dyDescent="0.4">
+      <c r="A5" s="12" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="3"/>
-      <c r="D3" s="3"/>
-      <c r="E3" s="3"/>
-      <c r="F3" s="3"/>
-    </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.55000000000000004">
-      <c r="A4" t="s">
+      <c r="B5" s="10"/>
+      <c r="C5" s="3"/>
+      <c r="D5" s="3"/>
+      <c r="E5" s="3"/>
+      <c r="F5" s="3"/>
+      <c r="G5" s="10"/>
+      <c r="H5" s="10"/>
+      <c r="I5" s="10"/>
+      <c r="J5" s="10"/>
+      <c r="K5" s="10"/>
+      <c r="L5" s="10"/>
+      <c r="M5" s="10"/>
+    </row>
+    <row r="6" spans="1:14" ht="18" x14ac:dyDescent="0.4">
+      <c r="A6" s="12"/>
+      <c r="B6" s="10"/>
+      <c r="C6" s="3"/>
+      <c r="D6" s="3"/>
+      <c r="E6" s="3"/>
+      <c r="F6" s="3"/>
+      <c r="G6" s="10"/>
+      <c r="H6" s="10"/>
+      <c r="I6" s="10"/>
+      <c r="J6" s="10"/>
+      <c r="K6" s="10"/>
+      <c r="L6" s="10"/>
+      <c r="M6" s="10"/>
+    </row>
+    <row r="7" spans="1:14" ht="36" x14ac:dyDescent="0.4">
+      <c r="A7" s="11" t="s">
         <v>2</v>
       </c>
-      <c r="E4" s="2"/>
-      <c r="F4" s="2"/>
-      <c r="G4" s="2"/>
-      <c r="H4" s="2"/>
-      <c r="I4" s="2"/>
-      <c r="J4" s="2"/>
-      <c r="K4" s="2"/>
-    </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.55000000000000004">
-      <c r="A5" t="s">
+      <c r="B7" s="10"/>
+      <c r="C7" s="10"/>
+      <c r="D7" s="10"/>
+      <c r="E7" s="4"/>
+      <c r="F7" s="4"/>
+      <c r="G7" s="4"/>
+      <c r="H7" s="4"/>
+      <c r="I7" s="4"/>
+      <c r="J7" s="4"/>
+      <c r="K7" s="4"/>
+      <c r="L7" s="10"/>
+      <c r="M7" s="10"/>
+    </row>
+    <row r="8" spans="1:14" ht="18" x14ac:dyDescent="0.4">
+      <c r="A8" s="12" t="s">
         <v>3</v>
       </c>
-      <c r="C5" s="1"/>
-      <c r="D5" s="1"/>
-      <c r="E5" s="1"/>
-      <c r="F5" s="1"/>
-      <c r="G5" s="1"/>
-      <c r="H5" s="1"/>
-      <c r="I5" s="1"/>
-      <c r="J5" s="1"/>
-    </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.55000000000000004">
-      <c r="A6" t="s">
+      <c r="B8" s="10"/>
+      <c r="C8" s="5"/>
+      <c r="D8" s="5"/>
+      <c r="E8" s="5"/>
+      <c r="F8" s="5"/>
+      <c r="G8" s="5"/>
+      <c r="H8" s="5"/>
+      <c r="I8" s="5"/>
+      <c r="J8" s="5"/>
+      <c r="K8" s="10"/>
+      <c r="L8" s="10"/>
+      <c r="M8" s="10"/>
+    </row>
+    <row r="9" spans="1:14" ht="18" x14ac:dyDescent="0.4">
+      <c r="A9" s="12"/>
+      <c r="B9" s="10"/>
+      <c r="C9" s="5"/>
+      <c r="D9" s="5"/>
+      <c r="E9" s="5"/>
+      <c r="F9" s="5"/>
+      <c r="G9" s="5"/>
+      <c r="H9" s="5"/>
+      <c r="I9" s="5"/>
+      <c r="J9" s="5"/>
+      <c r="K9" s="10"/>
+      <c r="L9" s="10"/>
+      <c r="M9" s="10"/>
+    </row>
+    <row r="10" spans="1:14" ht="36" x14ac:dyDescent="0.4">
+      <c r="A10" s="11" t="s">
         <v>4</v>
       </c>
-      <c r="B6" s="5"/>
-      <c r="C6" s="5"/>
-      <c r="D6" s="5"/>
-      <c r="E6" s="5"/>
-      <c r="F6" s="5"/>
-      <c r="G6" s="5"/>
-      <c r="H6" s="5"/>
-      <c r="I6" s="5"/>
-      <c r="J6" s="5"/>
-      <c r="K6" s="5"/>
-      <c r="L6" s="5"/>
-      <c r="M6" s="5"/>
-    </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.55000000000000004">
-      <c r="A7" t="s">
-        <v>17</v>
-      </c>
-      <c r="J7" s="6"/>
-      <c r="K7" s="6"/>
-      <c r="L7" s="6"/>
-      <c r="M7" s="6"/>
+      <c r="B10" s="6"/>
+      <c r="C10" s="6"/>
+      <c r="D10" s="6"/>
+      <c r="E10" s="6"/>
+      <c r="F10" s="6"/>
+      <c r="G10" s="6"/>
+      <c r="H10" s="6"/>
+      <c r="I10" s="6"/>
+      <c r="J10" s="6"/>
+      <c r="K10" s="6"/>
+      <c r="L10" s="6"/>
+      <c r="M10" s="6"/>
+    </row>
+    <row r="11" spans="1:14" ht="18" x14ac:dyDescent="0.4">
+      <c r="A11" s="12" t="s">
+        <v>5</v>
+      </c>
+      <c r="B11" s="10"/>
+      <c r="C11" s="10"/>
+      <c r="D11" s="10"/>
+      <c r="E11" s="10"/>
+      <c r="F11" s="10"/>
+      <c r="G11" s="10"/>
+      <c r="H11" s="10"/>
+      <c r="I11" s="10"/>
+      <c r="J11" s="7"/>
+      <c r="K11" s="7"/>
+      <c r="L11" s="7"/>
+      <c r="M11" s="7"/>
+    </row>
+    <row r="12" spans="1:14" ht="18" x14ac:dyDescent="0.4">
+      <c r="A12" s="12"/>
+      <c r="B12" s="10"/>
+      <c r="C12" s="10"/>
+      <c r="D12" s="10"/>
+      <c r="E12" s="10"/>
+      <c r="F12" s="10"/>
+      <c r="G12" s="10"/>
+      <c r="H12" s="10"/>
+      <c r="I12" s="10"/>
+      <c r="J12" s="7"/>
+      <c r="K12" s="7"/>
+      <c r="L12" s="7"/>
+      <c r="M12" s="7"/>
+    </row>
+    <row r="13" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A13" s="8"/>
+      <c r="B13" s="8"/>
     </row>
   </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="A3:A4"/>
+    <mergeCell ref="A5:A6"/>
+    <mergeCell ref="A8:A9"/>
+    <mergeCell ref="A11:A12"/>
+  </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
